--- a/data-raw/digitized_flipcharts_fairqual_workshop_itd24.xlsx
+++ b/data-raw/digitized_flipcharts_fairqual_workshop_itd24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/mohrf_ethz_ch/Documents/fairqual_workshop/further_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohrf/Downloads/fairqual/fairqual-dataitd24-2204e25/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{EEC1752C-5C3D-8B42-8BA5-961064F097C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7D215A2-23EB-40D2-BDA3-514F5554BC58}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5389E6-3E9F-704E-9B61-7A449D35D1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35660" yWindow="500" windowWidth="47880" windowHeight="26580" xr2:uid="{5E649C27-1281-1045-B8AB-F8E73E96FCE4}"/>
+    <workbookView xWindow="32120" yWindow="500" windowWidth="47880" windowHeight="26580" xr2:uid="{5E649C27-1281-1045-B8AB-F8E73E96FCE4}"/>
   </bookViews>
   <sheets>
     <sheet name="part_1" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="317">
   <si>
     <t>group</t>
   </si>
@@ -1057,7 +1057,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1443,16 +1443,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9F7307-B8C3-CE44-8B93-23E18C6DF282}">
   <dimension ref="A1:F218"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="56.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="1.625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="27.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.100000000000001">
+    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.100000000000001">
+    <row r="2" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17.100000000000001">
+    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.100000000000001">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="17.100000000000001">
+    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17.100000000000001">
+    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17.100000000000001">
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.100000000000001">
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.100000000000001">
+    <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17.100000000000001">
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17.100000000000001">
+    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17.100000000000001">
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17.100000000000001">
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17.100000000000001">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.100000000000001">
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="17.100000000000001">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17.100000000000001">
+    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="17.100000000000001">
+    <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17.100000000000001">
+    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.100000000000001">
+    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="33.950000000000003">
+    <row r="21" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="33.950000000000003">
+    <row r="22" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17.100000000000001">
+    <row r="23" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17.100000000000001">
+    <row r="24" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17.100000000000001">
+    <row r="25" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="17.100000000000001">
+    <row r="26" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="33.950000000000003">
+    <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="51">
+    <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="51">
+    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="33.950000000000003">
+    <row r="30" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="17.100000000000001">
+    <row r="31" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="33.950000000000003">
+    <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="17.100000000000001">
+    <row r="33" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="17.100000000000001">
+    <row r="34" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="33.950000000000003">
+    <row r="35" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="17.100000000000001">
+    <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="17.100000000000001">
+    <row r="37" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="17.100000000000001">
+    <row r="38" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="33.950000000000003">
+    <row r="39" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="51">
+    <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="33.950000000000003">
+    <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="33.950000000000003">
+    <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="33.950000000000003">
+    <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="33.950000000000003">
+    <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="33.950000000000003">
+    <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="33.950000000000003">
+    <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="17.100000000000001">
+    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="17.100000000000001">
+    <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="17.100000000000001">
+    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="33.950000000000003">
+    <row r="50" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="51">
+    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="17.100000000000001">
+    <row r="52" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="17.100000000000001">
+    <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="33.950000000000003">
+    <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="33.950000000000003">
+    <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="17.100000000000001">
+    <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="33.950000000000003">
+    <row r="57" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="33.950000000000003">
+    <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="17.100000000000001">
+    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="33.950000000000003">
+    <row r="60" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -2403,12 +2403,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="17.100000000000001">
+    <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B61">
-        <v>5</v>
+      <c r="B61" t="s">
+        <v>82</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>81</v>
@@ -2420,12 +2420,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="17.100000000000001">
+    <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>6</v>
       </c>
-      <c r="B62">
-        <v>5</v>
+      <c r="B62" t="s">
+        <v>82</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>81</v>
@@ -2437,7 +2437,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="17.100000000000001">
+    <row r="63" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>85</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="17.100000000000001">
+    <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>85</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="17.100000000000001">
+    <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>85</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="17.100000000000001">
+    <row r="66" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>85</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="17.100000000000001">
+    <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>85</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="17.100000000000001">
+    <row r="68" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>85</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="17.100000000000001">
+    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="17.100000000000001">
+    <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>85</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="17.100000000000001">
+    <row r="71" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="17.100000000000001">
+    <row r="72" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="17.100000000000001">
+    <row r="73" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="33.950000000000003">
+    <row r="74" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="17.100000000000001">
+    <row r="75" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="17.100000000000001">
+    <row r="76" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="33.950000000000003">
+    <row r="77" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="17.100000000000001">
+    <row r="78" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="17.100000000000001">
+    <row r="79" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="17.100000000000001">
+    <row r="80" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="17.100000000000001">
+    <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="17.100000000000001">
+    <row r="82" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="17.100000000000001">
+    <row r="83" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="17.100000000000001">
+    <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="17.100000000000001">
+    <row r="85" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="17.100000000000001">
+    <row r="86" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="17.100000000000001">
+    <row r="87" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>85</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="17.100000000000001">
+    <row r="88" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="33.950000000000003">
+    <row r="89" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="17.100000000000001">
+    <row r="90" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>85</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="17.100000000000001">
+    <row r="91" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="17.100000000000001">
+    <row r="92" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="33.950000000000003">
+    <row r="93" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>85</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="17.100000000000001">
+    <row r="94" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>85</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="17.100000000000001">
+    <row r="95" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="17.100000000000001">
+    <row r="96" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>85</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="33.950000000000003">
+    <row r="97" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="33.950000000000003">
+    <row r="98" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>85</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="17.100000000000001">
+    <row r="99" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>85</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="33.950000000000003">
+    <row r="100" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>85</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="17.100000000000001">
+    <row r="101" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>85</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="33.950000000000003">
+    <row r="102" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>85</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="51">
+    <row r="103" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>85</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="51">
+    <row r="104" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>85</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="51">
+    <row r="105" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>85</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="51">
+    <row r="106" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>85</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="33.950000000000003">
+    <row r="107" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>85</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="33.950000000000003">
+    <row r="108" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>85</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="33.950000000000003">
+    <row r="109" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>85</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="17.100000000000001">
+    <row r="110" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>85</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="33.950000000000003">
+    <row r="111" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>85</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="17.100000000000001">
+    <row r="112" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>85</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="17.100000000000001">
+    <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>85</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="17.100000000000001">
+    <row r="114" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>85</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="17.100000000000001">
+    <row r="115" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>85</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="33.950000000000003">
+    <row r="116" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>85</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="17.100000000000001">
+    <row r="117" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>160</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="17.100000000000001">
+    <row r="118" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>160</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="33.950000000000003">
+    <row r="119" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>160</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="17.100000000000001">
+    <row r="120" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>160</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="17.100000000000001">
+    <row r="121" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>160</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="33.950000000000003">
+    <row r="122" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>160</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="33.950000000000003">
+    <row r="123" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>160</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="33.950000000000003">
+    <row r="124" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>160</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="51">
+    <row r="125" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="33.950000000000003">
+    <row r="126" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>160</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="17.100000000000001">
+    <row r="127" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>160</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="17.100000000000001">
+    <row r="128" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>160</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="17.100000000000001">
+    <row r="129" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>160</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="33.950000000000003">
+    <row r="130" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>160</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="33.950000000000003">
+    <row r="131" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>160</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="33.950000000000003">
+    <row r="132" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="33.950000000000003">
+    <row r="133" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="17.100000000000001">
+    <row r="134" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>160</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="17.100000000000001">
+    <row r="135" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>160</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="33.950000000000003">
+    <row r="136" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>160</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="33.950000000000003">
+    <row r="137" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>160</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="17.100000000000001">
+    <row r="138" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>160</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="33.950000000000003">
+    <row r="139" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>160</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="33.950000000000003">
+    <row r="140" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>160</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="33.950000000000003">
+    <row r="141" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>160</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="33.950000000000003">
+    <row r="142" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>160</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="51">
+    <row r="143" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>160</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="17.100000000000001">
+    <row r="144" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="17.100000000000001">
+    <row r="145" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>160</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="17.100000000000001">
+    <row r="146" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="17.100000000000001">
+    <row r="147" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>160</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="68.099999999999994">
+    <row r="148" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>160</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="33.950000000000003">
+    <row r="149" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>160</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="17.100000000000001">
+    <row r="150" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>160</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="33.950000000000003">
+    <row r="151" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>160</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="33.950000000000003">
+    <row r="152" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>160</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="33.950000000000003">
+    <row r="153" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="17.100000000000001">
+    <row r="154" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>160</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="17.100000000000001">
+    <row r="155" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>160</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="17.100000000000001">
+    <row r="156" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="33.950000000000003">
+    <row r="157" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="51">
+    <row r="158" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="17.100000000000001">
+    <row r="159" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>160</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="33.950000000000003">
+    <row r="160" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="33.950000000000003">
+    <row r="161" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>160</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="17.100000000000001">
+    <row r="162" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>160</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="33.950000000000003">
+    <row r="163" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>160</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="17.100000000000001">
+    <row r="164" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>160</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="17.100000000000001">
+    <row r="165" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>160</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="17.100000000000001">
+    <row r="166" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>160</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="17.100000000000001">
+    <row r="167" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>160</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="17.100000000000001">
+    <row r="168" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>160</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="33.950000000000003">
+    <row r="169" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>160</v>
       </c>
@@ -4244,12 +4244,12 @@
         <v>242</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="17.100000000000001">
+    <row r="170" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>160</v>
       </c>
-      <c r="B170">
-        <v>5</v>
+      <c r="B170" t="s">
+        <v>82</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>81</v>
@@ -4261,12 +4261,12 @@
         <v>243</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="17.100000000000001">
+    <row r="171" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>160</v>
       </c>
-      <c r="B171">
-        <v>5</v>
+      <c r="B171" t="s">
+        <v>82</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>81</v>
@@ -4278,12 +4278,12 @@
         <v>244</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="17.100000000000001">
+    <row r="172" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>160</v>
       </c>
-      <c r="B172">
-        <v>5</v>
+      <c r="B172" t="s">
+        <v>82</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>81</v>
@@ -4295,7 +4295,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="17.100000000000001">
+    <row r="173" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>246</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="17.100000000000001">
+    <row r="174" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>246</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="17.100000000000001">
+    <row r="175" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>246</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="17.100000000000001">
+    <row r="176" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>246</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="17.100000000000001">
+    <row r="177" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>246</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="33.950000000000003">
+    <row r="178" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>246</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="17.100000000000001">
+    <row r="179" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>246</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="17.100000000000001">
+    <row r="180" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>246</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="17.100000000000001">
+    <row r="181" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>246</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="17.100000000000001">
+    <row r="182" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>246</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="17.100000000000001">
+    <row r="183" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>246</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="17.100000000000001">
+    <row r="184" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>246</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="17.100000000000001">
+    <row r="185" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>246</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="17.100000000000001">
+    <row r="186" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>246</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="17.100000000000001">
+    <row r="187" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>246</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="17.100000000000001">
+    <row r="188" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>246</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="17.100000000000001">
+    <row r="189" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>246</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="17.100000000000001">
+    <row r="190" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>246</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="17.100000000000001">
+    <row r="191" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>246</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="17.100000000000001">
+    <row r="192" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>246</v>
       </c>
@@ -4581,7 +4581,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="17.100000000000001">
+    <row r="193" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>246</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="17.100000000000001">
+    <row r="194" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>246</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="17.100000000000001">
+    <row r="195" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>246</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="33.950000000000003">
+    <row r="196" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>246</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="17.100000000000001">
+    <row r="197" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>246</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="33.950000000000003">
+    <row r="198" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>246</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="51">
+    <row r="199" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>246</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="17.100000000000001">
+    <row r="200" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>246</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="17.100000000000001">
+    <row r="201" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>246</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="17.100000000000001">
+    <row r="202" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>246</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="33.950000000000003">
+    <row r="203" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>246</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="17.100000000000001">
+    <row r="204" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>246</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="17.100000000000001">
+    <row r="205" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>246</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="33.950000000000003">
+    <row r="206" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>246</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="17.100000000000001">
+    <row r="207" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>246</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="33.950000000000003">
+    <row r="208" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>246</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="17.100000000000001">
+    <row r="209" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>246</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="17.100000000000001">
+    <row r="210" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>246</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="17.100000000000001">
+    <row r="211" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>246</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="17.100000000000001">
+    <row r="212" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>246</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="33.950000000000003">
+    <row r="213" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>246</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="17.100000000000001">
+    <row r="214" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>246</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="33.950000000000003">
+    <row r="215" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>246</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="17.100000000000001">
+    <row r="216" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>246</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="17.100000000000001">
+    <row r="217" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>246</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="33.950000000000003">
+    <row r="218" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>246</v>
       </c>
@@ -5004,13 +5004,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BEAD0D1-F236-634E-A8F7-6DA485BE71DC}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="32.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>303</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>303</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>303</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>303</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>311</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>311</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>311</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>311</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>311</v>
       </c>
@@ -5120,13 +5120,13 @@
         <v>316</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
     </row>
   </sheetData>
